--- a/test3.xlsx
+++ b/test3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B119C3-4E7E-4D90-A331-ACCE0C0070E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6882B37-2BF1-4AA6-9181-66D4981E7926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15210" yWindow="5010" windowWidth="14040" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12150" yWindow="3420" windowWidth="14040" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,72 +25,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>def add(x, y):
-  return x +y
-def subtract(x, y):
-  return x-y
-def multiply(x, y):
-  return x*y
-def divide(x, y):
-    if y == 0:
-        return "Деление на ноль невозможно"
-    else:
-      return x/y
-num1 = float(input())
-operator = input()
-num2 = float(input())
-if operator == '+':
-    result = add(num1, num2)
-elif operator == '-':
-    result = subtract(num1, num2)
-elif operator == '*':
-    result = multiply(num1, num2)
-elif operator == '/':
-    result = divide(num1, num2)
-else:
-    result = "Ошибка! Неправильная операция."
-print(result)</t>
-  </si>
-  <si>
-    <t>это блок кода, который выполняет определенную задачу или вычисление, имеет имя, и может быть вызван из другого места программы для повторного использования.</t>
-  </si>
-  <si>
-    <t>Параметры (аргументы)</t>
-  </si>
-  <si>
-    <t>Место в программе, где переменная доступна для использования.</t>
-  </si>
-  <si>
-    <t>Функция, которая возвращает значение после выполнения своей задачи.</t>
-  </si>
-  <si>
-    <t>length * width</t>
-  </si>
-  <si>
-    <t>label = Label(root, text='Hello World!')</t>
-  </si>
-  <si>
-    <t>Идея</t>
-  </si>
-  <si>
-    <t>Сеттинг</t>
-  </si>
-  <si>
-    <t>Арт-дизайн и художественный стиль</t>
-  </si>
-  <si>
-    <t>протагонист</t>
-  </si>
-  <si>
-    <t>Общая информация об игре</t>
-  </si>
-  <si>
-    <t>Лишнюю информацию, усложняющую восприятие документа.</t>
-  </si>
-  <si>
-    <t>Да, достаточно сохранить файл с именем модуля и расширением .py.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Правила взаимодействия игрока с виртуальным миром игры</t>
+  </si>
+  <si>
+    <t>Игроки часто сталкиваются с фрустрацией и разочарованием</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>HUD</t>
+  </si>
+  <si>
+    <t>Эмоциональный отклик пользователей от взаимодействия с продуктом</t>
+  </si>
+  <si>
+    <t>Минимальная единица цифрового изображения, представленная точкой определенного цвета.</t>
+  </si>
+  <si>
+    <t>Вход → Выбор блюд → Корзина → Оплата → Подтверждение</t>
+  </si>
+  <si>
+    <t>Последовательность шагов, которые игрок проходит от знакомства с игрой до завершения сессии.</t>
+  </si>
+  <si>
+    <t>Циклический алгоритм, повторяющий шаги игры: обновление состояния, обработку ввода и вывод на экран.</t>
+  </si>
+  <si>
+    <t>display</t>
+  </si>
+  <si>
+    <t>all_sprites.update() -&gt; обновление всех спрайтов
+pygame.quit() -&gt; Завершение работы библиотеки
+sprite.kill() -&gt; Удаление спрайта</t>
+  </si>
+  <si>
+    <t>Окно меняет размеры вслед за изменением размера экрана.</t>
+  </si>
+  <si>
+    <t>Красный (Red);</t>
+  </si>
+  <si>
+    <t>pygame.init()</t>
+  </si>
+  <si>
+    <t>screen</t>
   </si>
 </sst>
 </file>
@@ -413,90 +394,93 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B1">
-        <v>1178531</v>
+        <v>1178822</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B2">
-        <v>1178541</v>
+        <v>1178832</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B3">
-        <v>1178551</v>
+        <v>1178860</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B4">
-        <v>1178711</v>
+        <v>1178870</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B5">
-        <v>1178721</v>
+        <v>1178880</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B6">
-        <v>1178731</v>
+        <v>1178890</v>
       </c>
       <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2992</v>
+      </c>
+      <c r="B7">
+        <v>1178900</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2990</v>
-      </c>
-      <c r="B7">
-        <v>1178741</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B8">
-        <v>1178742</v>
+        <v>1178910</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -504,10 +488,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B9">
-        <v>1178752</v>
+        <v>1178920</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -515,68 +499,72 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B10">
-        <v>1178762</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1178930</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B11">
-        <v>1178772</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
+        <v>1178940</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B12">
-        <v>1178782</v>
+        <v>1178950</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B13">
-        <v>1178792</v>
+        <v>1178960</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B14">
-        <v>1178802</v>
+        <v>1178970</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="B15">
-        <v>1178812</v>
+        <v>1178980</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/test3.xlsx
+++ b/test3.xlsx
@@ -1,101 +1,480 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6882B37-2BF1-4AA6-9181-66D4981E7926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12150" yWindow="3420" windowWidth="14040" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14400" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Правила взаимодействия игрока с виртуальным миром игры</t>
-  </si>
-  <si>
-    <t>Игроки часто сталкиваются с фрустрацией и разочарованием</t>
-  </si>
-  <si>
-    <t>Нет</t>
-  </si>
-  <si>
-    <t>HUD</t>
-  </si>
-  <si>
-    <t>Эмоциональный отклик пользователей от взаимодействия с продуктом</t>
-  </si>
-  <si>
-    <t>Минимальная единица цифрового изображения, представленная точкой определенного цвета.</t>
-  </si>
-  <si>
-    <t>Вход → Выбор блюд → Корзина → Оплата → Подтверждение</t>
-  </si>
-  <si>
-    <t>Последовательность шагов, которые игрок проходит от знакомства с игрой до завершения сессии.</t>
-  </si>
-  <si>
-    <t>Циклический алгоритм, повторяющий шаги игры: обновление состояния, обработку ввода и вывод на экран.</t>
-  </si>
-  <si>
-    <t>display</t>
-  </si>
-  <si>
-    <t>all_sprites.update() -&gt; обновление всех спрайтов
-pygame.quit() -&gt; Завершение работы библиотеки
-sprite.kill() -&gt; Удаление спрайта</t>
-  </si>
-  <si>
-    <t>Окно меняет размеры вслед за изменением размера экрана.</t>
-  </si>
-  <si>
-    <t>Красный (Red);</t>
-  </si>
-  <si>
-    <t>pygame.init()</t>
-  </si>
-  <si>
-    <t>screen</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>Я успешно завершил обучение по третьему модулю программы и перехожу на следующий модуль курса.</t>
+  </si>
+  <si>
+    <t>Умный код на Python. Начальный уровень</t>
+  </si>
+  <si>
+    <t>Хочу попробывать что-то новое в ИТ, Просто интересно, чем занимаются в ИТ-сфере, выф</t>
+  </si>
+  <si>
+    <t>&lt;G&gt;</t>
+  </si>
+  <si>
+    <t>В колледже/техникуме, 4 курс</t>
+  </si>
+  <si>
+    <t>19-25 лет</t>
+  </si>
+  <si>
+    <t>Республика Дагестан</t>
+  </si>
+  <si>
+    <t>4-6 часов</t>
+  </si>
+  <si>
+    <t>Теоретический материал излагается четко и понятно</t>
+  </si>
+  <si>
+    <t>Материалы курса удобны для использования.</t>
+  </si>
+  <si>
+    <t>После прохождения модуля курса я чувствую себя увереннее в теме ИТ и занимаюсь интересом</t>
+  </si>
+  <si>
+    <t>Думаю, что ничего менять не нужно.</t>
+  </si>
+  <si>
+    <t>коллизия</t>
+  </si>
+  <si>
+    <t>Для уменьшения количества вычислений и использованных ресурсов.</t>
+  </si>
+  <si>
+    <t>Проверять столкновения персонажа с другими игровыми объектами</t>
+  </si>
+  <si>
+    <t>В левом верхнем</t>
+  </si>
+  <si>
+    <t>это все то, что пользователь видит на экране</t>
+  </si>
+  <si>
+    <t>спрайт</t>
+  </si>
+  <si>
+    <t>черный</t>
+  </si>
+  <si>
+    <t>При нажатии на кнопки пробел персонаж игры прыгает.</t>
+  </si>
+  <si>
+    <t>self.rect</t>
+  </si>
+  <si>
+    <t>Данная функция создаёт три переменные для кнопок сна, здоровья и еды,а затем отрисовывает их на экране</t>
+  </si>
+  <si>
+    <t>Из сети маленьких квадратиков-пикселей</t>
+  </si>
+  <si>
+    <t>pygame.draw.rect()</t>
+  </si>
+  <si>
+    <t>В файле const.py.</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>pygame.mixer.music.play()</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -103,27 +482,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -172,7 +834,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -207,7 +869,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -381,190 +1043,329 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B1">
-        <v>1178822</v>
+        <v>1208280</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B2">
-        <v>1178832</v>
+        <v>1208281</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B3">
-        <v>1178860</v>
+        <v>1208284</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B4">
-        <v>1178870</v>
+        <v>1208286</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B5">
-        <v>1178880</v>
+        <v>1208287</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B6">
-        <v>1178890</v>
+        <v>1208288</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B7">
-        <v>1178900</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>1208289</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B8">
-        <v>1178910</v>
+        <v>1208290</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B9">
-        <v>1178920</v>
+        <v>1208291</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B10">
-        <v>1178930</v>
+        <v>1208292</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B11">
-        <v>1178940</v>
-      </c>
-      <c r="C11" s="1" t="s">
+        <v>1208293</v>
+      </c>
+      <c r="C11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="B12">
-        <v>1178950</v>
-      </c>
-      <c r="C12" t="s">
+        <v>1208294</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>2988</v>
+      </c>
+      <c r="B13">
+        <v>1208295</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2992</v>
-      </c>
-      <c r="B13">
-        <v>1178960</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>2993</v>
+      </c>
+      <c r="B14">
+        <v>1179413</v>
+      </c>
+      <c r="C14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2992</v>
-      </c>
-      <c r="B14">
-        <v>1178970</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>2993</v>
+      </c>
+      <c r="B15">
+        <v>1179423</v>
+      </c>
+      <c r="C15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2992</v>
-      </c>
-      <c r="B15">
-        <v>1178980</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>2993</v>
+      </c>
+      <c r="B16">
+        <v>1179433</v>
+      </c>
+      <c r="C16" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>2993</v>
+      </c>
+      <c r="B17">
+        <v>1179443</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>2993</v>
+      </c>
+      <c r="B18">
+        <v>1179453</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>2993</v>
+      </c>
+      <c r="B19">
+        <v>1179463</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>2993</v>
+      </c>
+      <c r="B20">
+        <v>1179473</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>2993</v>
+      </c>
+      <c r="B21">
+        <v>1179483</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>2993</v>
+      </c>
+      <c r="B22">
+        <v>1179493</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>2993</v>
+      </c>
+      <c r="B23">
+        <v>1179503</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>2993</v>
+      </c>
+      <c r="B24">
+        <v>1179513</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>2993</v>
+      </c>
+      <c r="B25">
+        <v>1179523</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>2993</v>
+      </c>
+      <c r="B26">
+        <v>1179533</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>2993</v>
+      </c>
+      <c r="B27">
+        <v>1179543</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>2993</v>
+      </c>
+      <c r="B28">
+        <v>1179553</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/test3.xlsx
+++ b/test3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A9B6A9-85D9-4632-B73C-8442C8C07725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4950ACCC-01EA-4391-8629-72B3A8784BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,107 +31,229 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>text = font.render('START', True, (255, 255, 255))</t>
-  </si>
-  <si>
-    <t>print('Button clicked!')</t>
-  </si>
-  <si>
-    <t>Способ передачи истории через окружение, предметы и визуальные подсказки.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Верно</t>
   </si>
   <si>
-    <t>Объекты, меняющие своё состояние при взаимодействии игрока</t>
-  </si>
-  <si>
-    <t>яркими и выделенными графическими элементами</t>
-  </si>
-  <si>
     <t>шкала</t>
   </si>
   <si>
-    <t>Любые пользователи могут проверить продукт и оставить отзыв.</t>
-  </si>
-  <si>
-    <t>dis.blit(background_menu, (0, 0))</t>
-  </si>
-  <si>
-    <t>Закрытие окна приложения</t>
-  </si>
-  <si>
-    <t>update</t>
-  </si>
-  <si>
-    <t>is_music_playing</t>
-  </si>
-  <si>
-    <t>Показывает кнопки выбора для перезагрузки игры.</t>
-  </si>
-  <si>
-    <t>Button</t>
-  </si>
-  <si>
-    <t>Я успешно завершил обучение по четвёртому модулю программы и перехожу на следующий модуль курса.</t>
-  </si>
-  <si>
-    <t>Умный код на Python. Начальный уровень</t>
-  </si>
-  <si>
-    <t>Хочу получить знания и навыки для будущей работы/ учебы, выф</t>
-  </si>
-  <si>
-    <t>&lt;G&gt;</t>
-  </si>
-  <si>
-    <t>В колледже/техникуме, 4 курс</t>
-  </si>
-  <si>
-    <t>19 – 25 лет</t>
-  </si>
-  <si>
-    <t>Республика Дагестан</t>
-  </si>
-  <si>
-    <t>2–4 часа</t>
-  </si>
-  <si>
-    <t>Теоретический материал излагается четко и понятно.</t>
-  </si>
-  <si>
-    <t>Материалы курса удобны для использования.</t>
-  </si>
-  <si>
-    <t>Полученные на начальном этапе обучения знания и навыки применимы на практике в моей текущей деятельности/ учебе.</t>
-  </si>
-  <si>
-    <t>Думаю, что ничего менять не нужно.</t>
+    <t>Модуль для работы с музыкой и звуком в играх</t>
+  </si>
+  <si>
+    <t>Sound.play()</t>
+  </si>
+  <si>
+    <t>чиптюн</t>
+  </si>
+  <si>
+    <t>Сжатие файла</t>
+  </si>
+  <si>
+    <t>Тема испытаний -&gt; Тайнственная,
+Боевая тема -&gt;  Напряженная,
+Главная тема -&gt; Живая и динамичная,
+Интро -&gt; Мелодичная,
+Заключительная тема -&gt; Надежды и удовлетворение</t>
+  </si>
+  <si>
+    <t>Вокалоид</t>
+  </si>
+  <si>
+    <t>btn_rect = pygame.Rect((100, 100), (100, 50))</t>
+  </si>
+  <si>
+    <t>Передача истории и событий посредством окружения, декораций и деталей среды.</t>
+  </si>
+  <si>
+    <t>Четкими и ясно видимыми</t>
+  </si>
+  <si>
+    <t>Ограниченной группой специально приглашенных пользователей</t>
+  </si>
+  <si>
+    <t>Рисует фон меню на поверхности дисплея</t>
+  </si>
+  <si>
+    <t>Разработка концепции и правил игры</t>
+  </si>
+  <si>
+    <t>Точный план, ведущий к победе.</t>
+  </si>
+  <si>
+    <t># Ввод символа от пользователя
+char = input()
+# Множество гласных букв русского алфавита
+vowels = {'а', 'е', 'ё', 'и', 'о', 'у', 'э', 'ы', 'ю', 'я'}
+# Проверка и вывод результата
+if char in vowels:
+    print("Гласная буква")
+else:
+    print("Согласная буква")</t>
+  </si>
+  <si>
+    <t>upper()</t>
+  </si>
+  <si>
+    <t># Получаем список чисел от пользователя
+numbers = list(map(int, input().split()))
+# Суммируем чётные элементы
+total = 0
+for num in numbers:
+    if num % 2 == 0:  # проверка на чётность
+        total += num
+# Выводим результат
+print(total)</t>
+  </si>
+  <si>
+    <t>def</t>
+  </si>
+  <si>
+    <t>def reverse_string(s):
+    """
+    Переворачивает строку задом наперёд.
+    Параметры:
+    s (str): Входная строка
+    Возвращает:
+    str: Перевёрнутая строка
+    """
+    return s[::-1]
+# Примеры использования:
+print(reverse_string("hello"))    # olleh
+print(reverse_string("racecar"))  # racecar
+print(reverse_string("python"))   # nohtyp</t>
+  </si>
+  <si>
+    <t>Изучение поведения пользователей в игре.</t>
+  </si>
+  <si>
+    <t>Шаблон для создания объектов с заданными свойствами и поведением.</t>
+  </si>
+  <si>
+    <t>Основной механизм, непрерывно исполняемый в ходе игры, ответственный за обновление состояний и отображение на экране.</t>
+  </si>
+  <si>
+    <t>Методы, позволяющие создать впечатление объёма и глубины, несмотря на отсутствие реальной 3D-графики.</t>
+  </si>
+  <si>
+    <t>pygame.display.set_mode(size)</t>
+  </si>
+  <si>
+    <t>Прием повествования, при котором игроки узнают о сюжете через изучение окружения, архитектуры и декоративных элементов.</t>
+  </si>
+  <si>
+    <t>queue</t>
+  </si>
+  <si>
+    <t>Добиться максимального соответствия звуков реальных действий героя.</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>Тема курса сейчас актуальна и популярна</t>
+  </si>
+  <si>
+    <t>Существенно повысился</t>
+  </si>
+  <si>
+    <t>Помогают разобраться в предметах программы общего образования</t>
+  </si>
+  <si>
+    <t>Использование цифровых технологий в своей деятельности, Дополнительное образование в сфере цифровых технологий</t>
+  </si>
+  <si>
+    <t>В своей основной учебе</t>
+  </si>
+  <si>
+    <t>Информационные (цифровые) технологии</t>
+  </si>
+  <si>
+    <t>По специальности в сфере цифровых технологий</t>
+  </si>
+  <si>
+    <t>Да, хочу</t>
+  </si>
+  <si>
+    <t>Да, в полной мере</t>
+  </si>
+  <si>
+    <t>Позвонить в банк по официальному номеру и уточнить информацию</t>
+  </si>
+  <si>
+    <t>Хотя бы $15$ учеников брали и художественную, и учебную литературу</t>
+  </si>
+  <si>
+    <t>=$\\textrm{B}1^\\ast \\textrm{A}1$-$\\textrm{C}1$-$2$</t>
+  </si>
+  <si>
+    <t>П2</t>
+  </si>
+  <si>
+    <t>if s[i].lower() in {'a', 'e', 'i', 'o', 'u', 'y'}:</t>
+  </si>
+  <si>
+    <t>n = int(input())
+# Словарь для хранения зарплаты каждого курьера
+salary = {}
+for _ in range(n):
+    data = input().split()
+    t = int(data[0])          # время в минутах
+    g = data[1]               # тип груза
+    u = int(data[2])          # срочность (0 или 1)
+    r = int(data[3])          # признак "не дозвонился" (0 или 1)
+    name = data[4]            # имя курьера
+    dist = t  # t — километры (поскольку иначе не посчитать базовую оплату)
+    # Базовая оплата
+    pay = dist * 2
+    # Доплата за тип груза
+    if g == "маленький":
+        pay += 5
+    elif g == "средний":
+        pay += 15
+    elif g == "большой":
+        pay += 30
+    # Срочность
+    if u == 1:
+        pay += 10
+    # Не дозвонился с первого раза
+    if r == 1:
+        pay -= 5
+    if t &lt;= 30:
+        pay += 7
+    # Добавляем зарплату курьеру
+    if name in salary:
+        salary[name] += pay
+    else:
+        salary[name] = pay
+# Находим имя с максимальной зарплатой
+best_name = max(salary, key=salary.get)
+print(best_name)</t>
+  </si>
+  <si>
+    <t>Я полностью удовлетворен(а) участием в проекте</t>
+  </si>
+  <si>
+    <t>Бесплатность, Доступность</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Уже порекомендовал(а)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -163,10 +285,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -442,161 +567,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="3" max="3" width="47.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B1">
-        <v>1179397</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
+        <v>1179712</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B2">
-        <v>1179572</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>1179722</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B3">
-        <v>1179582</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>1179732</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B4">
-        <v>1179592</v>
+        <v>1179742</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="90">
       <c r="A5">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B5">
-        <v>1179602</v>
+        <v>1179752</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B6">
-        <v>1179612</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
+        <v>1179762</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B7">
-        <v>1179622</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
+        <v>1179772</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B8">
-        <v>1179632</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>1179782</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B9">
-        <v>1179642</v>
+        <v>1179792</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B10">
-        <v>1179652</v>
+        <v>1179802</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B11">
-        <v>1179662</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>1179812</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B12">
-        <v>1179672</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>1179822</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B13">
-        <v>1179682</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>1179832</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B14">
-        <v>1179692</v>
+        <v>1179842</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -604,160 +729,556 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B15">
-        <v>1179702</v>
-      </c>
-      <c r="C15" s="1" t="s">
+        <v>1179852</v>
+      </c>
+      <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B16">
-        <v>1209397</v>
+        <v>1203977</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B17">
-        <v>1209398</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>1204316</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="165">
       <c r="A18">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B18">
-        <v>1209399</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
+        <v>1204154</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B19">
-        <v>1209400</v>
+        <v>1204461</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="165">
       <c r="A20">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B20">
-        <v>1209401</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
+        <v>1204177</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B21">
-        <v>1209402</v>
-      </c>
-      <c r="C21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>1204498</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="240">
       <c r="A22">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B22">
-        <v>1209403</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>21</v>
+        <v>1204219</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B23">
-        <v>1209404</v>
+        <v>1204692</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B24">
-        <v>1209405</v>
+        <v>1204702</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B25">
-        <v>1209408</v>
+        <v>1204373</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B26">
-        <v>1209409</v>
+        <v>1204388</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B27">
-        <v>1209410</v>
-      </c>
-      <c r="C27">
-        <v>10</v>
+        <v>1204398</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2989</v>
+        <v>2996</v>
       </c>
       <c r="B28">
-        <v>1209411</v>
-      </c>
-      <c r="C28" t="s">
+        <v>1204413</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>2996</v>
+      </c>
+      <c r="B29">
+        <v>1204428</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>2996</v>
+      </c>
+      <c r="B30">
+        <v>1204445</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>3101</v>
+      </c>
+      <c r="B31">
+        <v>1223825</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>3101</v>
+      </c>
+      <c r="B32">
+        <v>1223829</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>3101</v>
+      </c>
+      <c r="B33">
+        <v>1223832</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>3101</v>
+      </c>
+      <c r="B34">
+        <v>1223838</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>3101</v>
+      </c>
+      <c r="B35">
+        <v>1223840</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>3101</v>
+      </c>
+      <c r="B36">
+        <v>1223841</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>3101</v>
+      </c>
+      <c r="B37">
+        <v>1223886</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>3101</v>
+      </c>
+      <c r="B38">
+        <v>1223843</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>3101</v>
+      </c>
+      <c r="B39">
+        <v>1223845</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>3101</v>
+      </c>
+      <c r="B40">
+        <v>1223847</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>3101</v>
+      </c>
+      <c r="B41">
+        <v>1223853</v>
+      </c>
+      <c r="C41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>3101</v>
+      </c>
+      <c r="B42">
+        <v>1223854</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>3101</v>
+      </c>
+      <c r="B43">
+        <v>1223883</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>3101</v>
+      </c>
+      <c r="B44">
+        <v>1223885</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>3101</v>
+      </c>
+      <c r="B45">
+        <v>1223887</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>3101</v>
+      </c>
+      <c r="B46">
+        <v>1223888</v>
+      </c>
+      <c r="C46">
+        <v>14382</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>3101</v>
+      </c>
+      <c r="B47">
+        <v>1223889</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>3101</v>
+      </c>
+      <c r="B48">
+        <v>1223890</v>
+      </c>
+      <c r="C48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>3101</v>
+      </c>
+      <c r="B49">
+        <v>1223813</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>3101</v>
+      </c>
+      <c r="B50">
+        <v>1223818</v>
+      </c>
+      <c r="C50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>3101</v>
+      </c>
+      <c r="B51">
+        <v>1223822</v>
+      </c>
+      <c r="C51">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>3101</v>
+      </c>
+      <c r="B52">
+        <v>1223823</v>
+      </c>
+      <c r="C52" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>3101</v>
+      </c>
+      <c r="B53">
+        <v>1223855</v>
+      </c>
+      <c r="C53">
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="409.5">
+      <c r="A54">
+        <v>3101</v>
+      </c>
+      <c r="B54">
+        <v>1223886</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>3101</v>
+      </c>
+      <c r="B55">
+        <v>1223895</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>3101</v>
+      </c>
+      <c r="B56">
+        <v>1223896</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>3101</v>
+      </c>
+      <c r="B57">
+        <v>1223897</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>3101</v>
+      </c>
+      <c r="B58">
+        <v>1223898</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>3101</v>
+      </c>
+      <c r="B59">
+        <v>1223899</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>3101</v>
+      </c>
+      <c r="B60">
+        <v>1223900</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>3101</v>
+      </c>
+      <c r="B61">
+        <v>1223901</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>3101</v>
+      </c>
+      <c r="B62">
+        <v>1223902</v>
+      </c>
+      <c r="C62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>3101</v>
+      </c>
+      <c r="B63">
+        <v>1223903</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>3101</v>
+      </c>
+      <c r="B64">
+        <v>1223904</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>